--- a/artfynd/A 42480-2022 artfynd.xlsx
+++ b/artfynd/A 42480-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42480-2022 artfynd.xlsx
+++ b/artfynd/A 42480-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74233945</v>
+        <v>104350628</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skyllbäcksmyrsområdet, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380484.8699542979</v>
+        <v>380469</v>
       </c>
       <c r="R2" t="n">
-        <v>6743436.14557038</v>
+        <v>6743412</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,16 +775,11 @@
         <v>74233926</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380556.8516319633</v>
+        <v>380557</v>
       </c>
       <c r="R3" t="n">
-        <v>6743569.986399597</v>
+        <v>6743570</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,16 +877,11 @@
         <v>74233931</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380554.9487352887</v>
+        <v>380555</v>
       </c>
       <c r="R4" t="n">
-        <v>6743600.815644549</v>
+        <v>6743601</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,19 +942,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,19 +972,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74233938</v>
+        <v>74233937</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1057,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380552.0613400036</v>
+        <v>380552</v>
       </c>
       <c r="R5" t="n">
-        <v>6743543.776044595</v>
+        <v>6743547</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,19 +1040,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,19 +1069,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74233946</v>
+        <v>74233938</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1169,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380481.7913374581</v>
+        <v>380552</v>
       </c>
       <c r="R6" t="n">
-        <v>6743431.853396845</v>
+        <v>6743544</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,19 +1137,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,16 +1169,11 @@
         <v>74233939</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380560.0570666679</v>
+        <v>380560</v>
       </c>
       <c r="R7" t="n">
-        <v>6743534.229812324</v>
+        <v>6743534</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,19 +1234,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,19 +1263,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74233944</v>
+        <v>74233940</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1393,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380476.8578529944</v>
+        <v>380585</v>
       </c>
       <c r="R8" t="n">
-        <v>6743445.204416359</v>
+        <v>6743492</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1426,19 +1331,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,19 +1360,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74233943</v>
+        <v>74233941</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1505,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380485.1640019133</v>
+        <v>380600</v>
       </c>
       <c r="R9" t="n">
-        <v>6743444.926250056</v>
+        <v>6743475</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,19 +1428,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,37 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74233896</v>
+        <v>74233943</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380559.0309193489</v>
+        <v>380485</v>
       </c>
       <c r="R10" t="n">
-        <v>6743532.799108232</v>
+        <v>6743445</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,19 +1525,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,19 +1554,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74233937</v>
+        <v>74233944</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1729,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380552.1756287041</v>
+        <v>380477</v>
       </c>
       <c r="R11" t="n">
-        <v>6743547.190652589</v>
+        <v>6743445</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,19 +1622,9 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,19 +1651,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104350627</v>
+        <v>74233945</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1837,17 +1682,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>Skyllbäcksmyrsområdet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380543.7252909878</v>
+        <v>380485</v>
       </c>
       <c r="R12" t="n">
-        <v>6743572.379132469</v>
+        <v>6743436</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,22 +1716,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,27 +1736,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105000902</v>
+        <v>74233946</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,37 +1759,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ömtbergstjärn, SSV om, Vrm</t>
+          <t>Skyllbäcksmyrsområdet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380527.1572697227</v>
+        <v>380482</v>
       </c>
       <c r="R13" t="n">
-        <v>6743515.79703623</v>
+        <v>6743432</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,29 +1811,14 @@
           <t>Dalby</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>S-Tor-0336</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,28 +1829,415 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>anders tedeholm</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104350627</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norr om Ömtberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>380543</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6743572</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74233896</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skyllbäcksmyrsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>380559</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6743533</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74233910</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skyllbäcksmyrsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>380577</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6743599</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Jobbkryss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104350075</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N om Ömtbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>380527</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6743516</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42480-2022 artfynd.xlsx
+++ b/artfynd/A 42480-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233931</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233937</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1163,6 +1188,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233938</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1357,6 +1392,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233940</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1454,6 +1494,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233941</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233943</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1648,6 +1698,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233944</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1745,6 +1800,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1842,6 +1902,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233946</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1939,6 +2004,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2036,6 +2106,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233896</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
           <t>Jobbkryss</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74233910</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,8 +2318,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>